--- a/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146A62CC-B87A-4D94-B59E-76889275F33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{146A62CC-B87A-4D94-B59E-76889275F33D}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView activeTab="1" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
   </bookViews>
   <sheets>
-    <sheet name="BFLU" sheetId="1" r:id="rId1"/>
-    <sheet name="BFLUError" sheetId="2" r:id="rId2"/>
+    <sheet name="BFLU" r:id="rId1" sheetId="1"/>
+    <sheet name="BFLUError" r:id="rId2" sheetId="2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="131">
   <si>
     <t>Result</t>
   </si>
@@ -327,12 +327,118 @@
   </si>
   <si>
     <t>Thu Feb 05 00:45:35 IST 2026</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Tue Feb 17 11:51:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 11:51:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 11:52:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 11:53:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 11:53:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 11:54:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 11:54:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 11:55:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 11:55:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 11:56:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 11:56:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 11:57:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 11:58:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 11:58:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 11:59:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 11:59:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:00:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:00:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:01:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:01:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:02:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:03:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:03:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:06:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:07:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:07:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:08:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:08:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:09:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:09:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:10:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:10:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:11:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:11:49 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -391,42 +497,42 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -443,10 +549,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -481,7 +587,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -533,7 +639,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -644,21 +750,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -675,7 +781,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -747,27 +853,27 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
   <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.36328125" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="26.54296875" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="35.453125" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="18.7265625" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.453125" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="10.6328125" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="26.54296875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="7.6328125" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="7.6328125" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="27.90625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" width="6.36328125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" width="26.54296875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="35.453125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" width="18.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" width="9.453125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" width="10.6328125" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="26.54296875" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" width="7.6328125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" width="7.6328125" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="27.90625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -805,12 +911,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
@@ -825,12 +931,12 @@
         <v>50020006</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -845,12 +951,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -865,12 +971,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -885,12 +991,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
@@ -905,12 +1011,12 @@
         <v>282719</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
@@ -925,12 +1031,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
         <v>33</v>
@@ -945,12 +1051,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
         <v>22</v>
@@ -968,12 +1074,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
@@ -991,12 +1097,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
@@ -1014,12 +1120,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+    <row ht="25.5" r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>25</v>
@@ -1040,12 +1146,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="C13" t="s">
         <v>16</v>
@@ -1075,12 +1181,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
@@ -1098,12 +1204,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="C15" t="s">
         <v>26</v>
@@ -1121,12 +1227,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+    <row ht="25.5" r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>27</v>
@@ -1144,12 +1250,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="C17" t="s">
         <v>29</v>
@@ -1167,12 +1273,12 @@
         <v>282719</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
@@ -1190,12 +1296,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -1213,12 +1319,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="C20" t="s">
         <v>34</v>
@@ -1236,12 +1342,12 @@
         <v>282719</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="C21" t="s">
         <v>35</v>
@@ -1259,12 +1365,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="C22" t="s">
         <v>36</v>
@@ -1282,12 +1388,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="C23" t="s">
         <v>37</v>
@@ -1305,12 +1411,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="C24" t="s">
         <v>38</v>
@@ -1330,32 +1436,32 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:L12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.08984375" style="6" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="10.36328125" style="8" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="24.08984375" style="9" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="18.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="6.6328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="9.81640625" style="6" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="15.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="7.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="6.6328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="6.90625" style="6" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="45.1796875" style="8" customWidth="1" collapsed="1"/>
-    <col min="13" max="16384" width="8.7265625" style="6" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="6" width="6.08984375" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="8" width="10.36328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="9" width="24.08984375" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="6" width="7.81640625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="6" width="18.453125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="6" width="6.6328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="6" width="9.81640625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="6" width="15.54296875" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="6" width="6.6328125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="6" width="6.90625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="8" width="45.1796875" collapsed="true"/>
+    <col min="13" max="16384" style="6" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1393,12 +1499,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>67</v>
+      <c r="B2" t="s">
+        <v>120</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>41</v>
@@ -1416,12 +1522,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>68</v>
+      <c r="B3" t="s">
+        <v>121</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>42</v>
@@ -1439,12 +1545,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>69</v>
+      <c r="B4" t="s">
+        <v>122</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>43</v>
@@ -1462,12 +1568,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>44</v>
@@ -1485,12 +1591,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>70</v>
+      <c r="B6" t="s">
+        <v>124</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>45</v>
@@ -1508,12 +1614,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>46</v>
@@ -1531,12 +1637,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>47</v>
@@ -1554,12 +1660,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>71</v>
+      <c r="B9" t="s">
+        <v>127</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>48</v>
@@ -1580,12 +1686,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>72</v>
+      <c r="B10" t="s">
+        <v>128</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>49</v>
@@ -1606,12 +1712,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>50</v>
@@ -1632,12 +1738,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>51</v>
@@ -1659,7 +1765,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{146A62CC-B87A-4D94-B59E-76889275F33D}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44146F4B-CA0D-466B-89DE-35F65407B60C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="1" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
-    <sheet name="BFLU" r:id="rId1" sheetId="1"/>
-    <sheet name="BFLUError" r:id="rId2" sheetId="2"/>
+    <sheet name="BFLU" sheetId="1" r:id="rId1"/>
+    <sheet name="BFLUError" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="97">
   <si>
     <t>Result</t>
   </si>
@@ -200,15 +200,6 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Tue Feb 03 17:55:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 13:02:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 13:04:14 IST 2026</t>
-  </si>
-  <si>
     <t>aaa</t>
   </si>
   <si>
@@ -233,212 +224,118 @@
     <t>aa4</t>
   </si>
   <si>
-    <t>Wed Feb 04 13:09:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 13:12:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 13:13:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 13:19:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 13:20:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 13:20:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 13:24:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 13:26:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 13:27:06 IST 2026</t>
-  </si>
-  <si>
     <t>aad123</t>
   </si>
   <si>
-    <t>Wed Feb 04 23:39:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 23:40:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 23:41:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 23:41:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 23:42:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 23:42:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 23:43:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 23:43:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 23:44:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 23:44:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 23:45:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 23:46:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 23:46:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 23:47:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 23:47:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 23:48:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 23:52:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 05 00:43:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 05 00:43:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 05 00:44:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 05 00:44:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 05 00:45:35 IST 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Tue Feb 17 11:51:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 11:51:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 11:52:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 11:53:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 11:53:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 11:54:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 11:54:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 11:55:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 11:55:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 11:56:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 11:56:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 11:57:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 11:58:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 11:58:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 11:59:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 11:59:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:00:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:00:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:01:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:01:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:02:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:03:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:03:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:06:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:07:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:07:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:08:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:08:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:09:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:09:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:10:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:10:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:11:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:11:49 IST 2026</t>
+    <t>Mon Feb 23 15:02:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:03:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:06:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:06:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:09:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:11:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:17:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:18:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:19:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:23:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:27:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:29:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:36:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:37:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:40:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:41:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:43:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:44:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:48:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:48:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:49:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:53:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 15:54:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 16:36:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 16:41:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 16:44:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 16:45:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 16:47:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 16:48:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:04:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:07:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:10:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:12:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:13:09 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -497,42 +394,41 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -549,10 +445,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -587,7 +483,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -639,7 +535,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -750,21 +646,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -781,7 +677,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -853,27 +749,27 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
   <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="6.36328125" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="26.54296875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" width="35.453125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" width="18.7265625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" width="9.453125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" width="10.6328125" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="26.54296875" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" width="7.6328125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" width="7.6328125" collapsed="true"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="27.90625" collapsed="true"/>
+    <col min="1" max="1" width="6.36328125" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="26.54296875" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="35.453125" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="18.7265625" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.453125" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="10.6328125" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="26.54296875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="7.6328125" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="7.6328125" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="27.90625" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -911,12 +807,12 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="13" r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
@@ -931,12 +827,12 @@
         <v>50020006</v>
       </c>
     </row>
-    <row ht="13" r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -951,12 +847,12 @@
         <v>11</v>
       </c>
     </row>
-    <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -971,12 +867,12 @@
         <v>12</v>
       </c>
     </row>
-    <row ht="13" r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -991,12 +887,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="13" r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
@@ -1011,12 +907,12 @@
         <v>282719</v>
       </c>
     </row>
-    <row ht="13" r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
@@ -1031,12 +927,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row ht="13" r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
         <v>33</v>
@@ -1051,12 +947,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row ht="13" r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
         <v>22</v>
@@ -1074,12 +970,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row ht="13" r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
@@ -1097,12 +993,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row ht="13" r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
@@ -1120,12 +1016,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row ht="25.5" r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>25</v>
@@ -1146,12 +1042,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row ht="13" r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
         <v>16</v>
@@ -1181,12 +1077,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row ht="13" r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
@@ -1204,12 +1100,12 @@
         <v>11</v>
       </c>
     </row>
-    <row ht="13" r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
         <v>26</v>
@@ -1227,12 +1123,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="25.5" r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>27</v>
@@ -1250,12 +1146,12 @@
         <v>12</v>
       </c>
     </row>
-    <row ht="13" r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
         <v>29</v>
@@ -1273,12 +1169,12 @@
         <v>282719</v>
       </c>
     </row>
-    <row ht="13" r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
@@ -1296,12 +1192,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row ht="13" r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -1319,12 +1215,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row ht="13" r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
         <v>34</v>
@@ -1342,12 +1238,12 @@
         <v>282719</v>
       </c>
     </row>
-    <row ht="13" r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
         <v>35</v>
@@ -1365,12 +1261,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row ht="13" r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
         <v>36</v>
@@ -1388,12 +1284,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row ht="13" r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
         <v>37</v>
@@ -1411,12 +1307,12 @@
         <v>12</v>
       </c>
     </row>
-    <row ht="13" r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
         <v>38</v>
@@ -1436,32 +1332,32 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:M12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="6" width="6.08984375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="8" width="10.36328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="9" width="24.08984375" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="6" width="7.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="6" width="18.453125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="6" width="6.6328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="6" width="9.81640625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="6" width="15.54296875" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="6" width="6.6328125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="6" width="6.90625" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="8" width="45.1796875" collapsed="true"/>
-    <col min="13" max="16384" style="6" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.08984375" style="6" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="10.36328125" style="8" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="24.08984375" style="9" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="18.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="6.6328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="9.81640625" style="6" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="15.54296875" style="6" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="7.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="6.6328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="6.90625" style="6" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="45.1796875" style="8" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="8.7265625" style="6" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="25" r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1499,12 +1395,12 @@
         <v>15</v>
       </c>
     </row>
-    <row ht="25" r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>41</v>
@@ -1516,18 +1412,18 @@
         <v>10</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row ht="25" r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>42</v>
@@ -1539,18 +1435,18 @@
         <v>10</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row ht="25" r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>43</v>
@@ -1562,18 +1458,18 @@
         <v>10</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row ht="25" r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>44</v>
@@ -1585,18 +1481,18 @@
         <v>10</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row ht="25" r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>45</v>
@@ -1608,18 +1504,18 @@
         <v>10</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row ht="25" r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>46</v>
@@ -1631,18 +1527,18 @@
         <v>10</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row ht="25" r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>47</v>
@@ -1654,18 +1550,18 @@
         <v>10</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="L8" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row ht="37.5" r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>48</v>
@@ -1680,18 +1576,18 @@
         <v>282719</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="L9" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row ht="25" r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>49</v>
@@ -1706,18 +1602,18 @@
         <v>282719</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L10" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row ht="37.5" r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>50</v>
@@ -1738,12 +1634,12 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="37.5" r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>51</v>
@@ -1765,7 +1661,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44146F4B-CA0D-466B-89DE-35F65407B60C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{DC0CF45D-B66F-4F1A-BDA9-0FDAB61EBE07}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
   </bookViews>
   <sheets>
-    <sheet name="BFLU" sheetId="1" r:id="rId1"/>
-    <sheet name="BFLUError" sheetId="2" r:id="rId2"/>
+    <sheet name="BFLU" r:id="rId1" sheetId="1"/>
+    <sheet name="BFLUError" r:id="rId2" sheetId="2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="101">
   <si>
     <t>Result</t>
   </si>
@@ -227,115 +227,128 @@
     <t>aad123</t>
   </si>
   <si>
-    <t>Mon Feb 23 15:02:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:03:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:06:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:06:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:09:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:11:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:17:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:18:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:19:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:23:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:27:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:29:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:36:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:37:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:40:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:41:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:43:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:44:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:48:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:48:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:49:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:53:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 15:54:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 16:36:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 16:41:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 16:44:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 16:45:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 16:47:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 16:48:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:04:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:07:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:10:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:12:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:13:09 IST 2026</t>
+    <t>Mon Mar 09 17:43:51 IST 2026</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Mon Mar 09 19:16:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Mar 09 19:17:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Mar 09 20:55:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:28:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:29:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:30:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:30:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:31:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:31:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:32:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:33:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:33:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:34:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:34:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:35:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:36:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:36:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:37:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:38:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:38:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:39:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:39:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:40:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:41:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:41:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 14:42:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 16:28:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 16:29:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 16:30:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 16:31:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 16:31:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 16:32:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 16:32:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 16:33:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 16:34:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 16:34:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 16:35:36 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -394,41 +407,41 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -445,10 +458,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -483,7 +496,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -535,7 +548,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -646,21 +659,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -677,7 +690,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -749,27 +762,27 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
   <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.36328125" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="26.54296875" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="35.453125" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="18.7265625" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.453125" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="10.6328125" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="26.54296875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="7.6328125" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="7.6328125" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="27.90625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" width="6.36328125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" width="26.54296875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="35.453125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" width="18.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" width="9.453125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" width="10.6328125" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="26.54296875" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" width="7.6328125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" width="7.6328125" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="27.90625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -807,12 +820,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
@@ -827,12 +840,12 @@
         <v>50020006</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -847,12 +860,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -867,12 +880,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -887,12 +900,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
@@ -907,12 +920,12 @@
         <v>282719</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
@@ -927,12 +940,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
         <v>33</v>
@@ -947,12 +960,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
         <v>22</v>
@@ -970,12 +983,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
@@ -993,12 +1006,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
@@ -1016,12 +1029,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+    <row ht="25.5" r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>25</v>
@@ -1042,12 +1055,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
         <v>16</v>
@@ -1077,12 +1090,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
@@ -1100,12 +1113,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
         <v>26</v>
@@ -1123,12 +1136,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+    <row ht="25.5" r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>27</v>
@@ -1146,12 +1159,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="17" spans="3:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
         <v>29</v>
@@ -1169,12 +1182,12 @@
         <v>282719</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="18" spans="3:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
@@ -1192,12 +1205,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="19" spans="3:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -1215,12 +1228,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="20" spans="3:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
         <v>34</v>
@@ -1238,12 +1251,12 @@
         <v>282719</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="21" spans="3:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
         <v>35</v>
@@ -1261,12 +1274,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="22" spans="3:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
         <v>36</v>
@@ -1284,12 +1297,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="23" spans="3:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
         <v>37</v>
@@ -1307,12 +1320,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="24" spans="3:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
         <v>38</v>
@@ -1332,32 +1345,32 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:L12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.08984375" style="6" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="10.36328125" style="8" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="24.08984375" style="9" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="18.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="6.6328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="9.81640625" style="6" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="15.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="7.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="6.6328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="6.90625" style="6" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="45.1796875" style="8" customWidth="1" collapsed="1"/>
-    <col min="13" max="16384" width="8.7265625" style="6" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="6" width="6.08984375" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="8" width="10.36328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="9" width="24.08984375" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="6" width="7.81640625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="6" width="18.453125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="6" width="6.6328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="6" width="9.81640625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="6" width="15.54296875" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="6" width="6.6328125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="6" width="6.90625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="8" width="45.1796875" collapsed="true"/>
+    <col min="13" max="16384" style="6" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1395,12 +1408,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>41</v>
@@ -1418,12 +1431,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>42</v>
@@ -1441,12 +1454,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>43</v>
@@ -1464,12 +1477,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>44</v>
@@ -1487,12 +1500,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>45</v>
@@ -1510,12 +1523,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>46</v>
@@ -1533,12 +1546,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>47</v>
@@ -1556,12 +1569,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>48</v>
@@ -1582,12 +1595,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>49</v>
@@ -1608,12 +1621,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>50</v>
@@ -1634,12 +1647,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>51</v>
@@ -1661,7 +1674,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{DC0CF45D-B66F-4F1A-BDA9-0FDAB61EBE07}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69211089-82A4-49BA-8ABF-994FAC3903E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
-    <sheet name="BFLU" r:id="rId1" sheetId="1"/>
-    <sheet name="BFLUError" r:id="rId2" sheetId="2"/>
+    <sheet name="BFLU" sheetId="1" r:id="rId1"/>
+    <sheet name="BFLUError" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="96">
   <si>
     <t>Result</t>
   </si>
@@ -227,128 +227,112 @@
     <t>aad123</t>
   </si>
   <si>
-    <t>Mon Mar 09 17:43:51 IST 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Mon Mar 09 19:16:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Mar 09 19:17:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Mar 09 20:55:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:28:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:29:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:30:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:30:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:31:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:31:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:32:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:33:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:33:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:34:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:34:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:35:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:36:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:36:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:37:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:38:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:38:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:39:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:39:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:40:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:41:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:41:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 14:42:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:28:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:29:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:30:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:31:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:31:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:32:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:32:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:33:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:34:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:34:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:35:36 IST 2026</t>
+    <t>Wed Mar 25 16:26:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:26:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:27:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:27:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:28:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:29:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:29:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:30:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:30:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:31:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:31:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:32:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:33:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:33:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:34:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:34:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:35:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:35:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:36:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:36:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:37:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:37:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:38:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:39:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:39:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:40:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:40:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:41:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:41:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:42:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:42:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:43:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:47:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:54:29 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -407,41 +391,41 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -458,10 +442,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -496,7 +480,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -548,7 +532,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -659,21 +643,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -690,7 +674,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -762,27 +746,27 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
   <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="6.36328125" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="26.54296875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" width="35.453125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" width="18.7265625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" width="9.453125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" width="10.6328125" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="26.54296875" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" width="7.6328125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" width="7.6328125" collapsed="true"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="27.90625" collapsed="true"/>
+    <col min="1" max="1" width="6.36328125" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="26.54296875" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="35.453125" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="18.7265625" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.453125" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="10.6328125" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="26.54296875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="7.6328125" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="7.6328125" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="27.90625" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -820,12 +804,12 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="13" r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
@@ -840,12 +824,12 @@
         <v>50020006</v>
       </c>
     </row>
-    <row ht="13" r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -860,12 +844,12 @@
         <v>11</v>
       </c>
     </row>
-    <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -880,12 +864,12 @@
         <v>12</v>
       </c>
     </row>
-    <row ht="13" r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -900,12 +884,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="13" r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
@@ -920,12 +904,12 @@
         <v>282719</v>
       </c>
     </row>
-    <row ht="13" r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
@@ -940,12 +924,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row ht="13" r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
         <v>33</v>
@@ -960,12 +944,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row ht="13" r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
         <v>22</v>
@@ -983,12 +967,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row ht="13" r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
@@ -1006,12 +990,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row ht="13" r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
@@ -1029,12 +1013,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row ht="25.5" r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>25</v>
@@ -1055,12 +1039,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row ht="13" r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
         <v>16</v>
@@ -1090,12 +1074,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row ht="13" r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
@@ -1113,12 +1097,12 @@
         <v>11</v>
       </c>
     </row>
-    <row ht="13" r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
         <v>26</v>
@@ -1136,12 +1120,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="25.5" r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>27</v>
@@ -1159,12 +1143,12 @@
         <v>12</v>
       </c>
     </row>
-    <row ht="13" r="17" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
         <v>29</v>
@@ -1182,12 +1166,12 @@
         <v>282719</v>
       </c>
     </row>
-    <row ht="13" r="18" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
@@ -1205,12 +1189,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row ht="13" r="19" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -1228,12 +1212,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row ht="13" r="20" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
         <v>34</v>
@@ -1251,12 +1235,12 @@
         <v>282719</v>
       </c>
     </row>
-    <row ht="13" r="21" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
         <v>35</v>
@@ -1274,12 +1258,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row ht="13" r="22" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
         <v>36</v>
@@ -1297,12 +1281,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row ht="13" r="23" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
         <v>37</v>
@@ -1320,12 +1304,12 @@
         <v>12</v>
       </c>
     </row>
-    <row ht="13" r="24" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
         <v>38</v>
@@ -1345,32 +1329,32 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:M12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="6" width="6.08984375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="8" width="10.36328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="9" width="24.08984375" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="6" width="7.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="6" width="18.453125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="6" width="6.6328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="6" width="9.81640625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="6" width="15.54296875" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="6" width="6.6328125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="6" width="6.90625" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="8" width="45.1796875" collapsed="true"/>
-    <col min="13" max="16384" style="6" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.08984375" style="6" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="10.36328125" style="8" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="24.08984375" style="9" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="18.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="6.6328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="9.81640625" style="6" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="15.54296875" style="6" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="7.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="6.6328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="6.90625" style="6" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="45.1796875" style="8" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="8.7265625" style="6" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="25" r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1408,12 +1392,12 @@
         <v>15</v>
       </c>
     </row>
-    <row ht="25" r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>41</v>
@@ -1431,12 +1415,12 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="25" r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>42</v>
@@ -1454,12 +1438,12 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="25" r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>43</v>
@@ -1477,12 +1461,12 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="25" r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>44</v>
@@ -1500,12 +1484,12 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="25" r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>45</v>
@@ -1523,12 +1507,12 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="25" r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>46</v>
@@ -1546,12 +1530,12 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="25" r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>47</v>
@@ -1569,12 +1553,12 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="37.5" r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>48</v>
@@ -1595,12 +1579,12 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="25" r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>49</v>
@@ -1621,12 +1605,12 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="37.5" r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>50</v>
@@ -1647,12 +1631,12 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="37.5" r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>51</v>
@@ -1674,7 +1658,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69211089-82A4-49BA-8ABF-994FAC3903E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DAC9DAD-98AD-4914-90B7-E2BB443F241E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
     <sheet name="BFLU" sheetId="1" r:id="rId1"/>
@@ -1340,7 +1340,7 @@
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.08984375" style="6" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="10.36328125" style="8" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="12.08984375" style="8" customWidth="1" collapsed="1"/>
     <col min="3" max="3" width="24.08984375" style="9" customWidth="1" collapsed="1"/>
     <col min="4" max="4" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
     <col min="5" max="5" width="18.453125" style="6" customWidth="1" collapsed="1"/>

--- a/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DAC9DAD-98AD-4914-90B7-E2BB443F241E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{9DAC9DAD-98AD-4914-90B7-E2BB443F241E}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
   </bookViews>
   <sheets>
-    <sheet name="BFLU" sheetId="1" r:id="rId1"/>
-    <sheet name="BFLUError" sheetId="2" r:id="rId2"/>
+    <sheet name="BFLU" r:id="rId1" sheetId="1"/>
+    <sheet name="BFLUError" r:id="rId2" sheetId="2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="150">
   <si>
     <t>Result</t>
   </si>
@@ -327,12 +327,175 @@
   </si>
   <si>
     <t>Wed Mar 25 16:54:29 IST 2026</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 12:50:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 12:53:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 12:56:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 12:59:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 13:02:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 13:05:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 13:08:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 13:11:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 13:14:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 13:17:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 13:21:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 13:25:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 13:30:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 13:33:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 13:37:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 13:40:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 13:44:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 13:47:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:03:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:04:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:05:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:06:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:06:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:07:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:08:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:08:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:09:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:10:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:10:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:11:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:12:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:12:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:13:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:14:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:14:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:15:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:15:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:16:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:17:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:17:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:18:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:18:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:19:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:20:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:21:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:21:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:22:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:22:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:23:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:23:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:24:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:24:59 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -391,41 +554,41 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -442,10 +605,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -480,7 +643,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -532,7 +695,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -643,21 +806,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -674,7 +837,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -746,27 +909,27 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
   <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.36328125" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="26.54296875" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="35.453125" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="18.7265625" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.453125" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="10.6328125" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="26.54296875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="7.6328125" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="7.6328125" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="27.90625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" width="6.36328125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" width="26.54296875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="35.453125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" width="18.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" width="9.453125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" width="10.6328125" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="26.54296875" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" width="7.6328125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" width="7.6328125" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="27.90625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -804,12 +967,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
@@ -824,12 +987,12 @@
         <v>50020006</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -844,12 +1007,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -864,12 +1027,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>119</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -884,12 +1047,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
@@ -904,12 +1067,12 @@
         <v>282719</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
@@ -924,12 +1087,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="C8" t="s">
         <v>33</v>
@@ -944,12 +1107,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="C9" t="s">
         <v>22</v>
@@ -967,12 +1130,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
@@ -990,12 +1153,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
@@ -1013,12 +1176,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+    <row ht="25.5" r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>25</v>
@@ -1039,12 +1202,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="C13" t="s">
         <v>16</v>
@@ -1074,12 +1237,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
@@ -1097,12 +1260,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="C15" t="s">
         <v>26</v>
@@ -1120,12 +1283,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+    <row ht="25.5" r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>27</v>
@@ -1143,12 +1306,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="C17" t="s">
         <v>29</v>
@@ -1166,12 +1329,12 @@
         <v>282719</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
@@ -1189,12 +1352,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -1212,12 +1375,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="C20" t="s">
         <v>34</v>
@@ -1235,12 +1398,12 @@
         <v>282719</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="C21" t="s">
         <v>35</v>
@@ -1258,12 +1421,12 @@
         <v>884777</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="C22" t="s">
         <v>36</v>
@@ -1281,12 +1444,12 @@
         <v>915029</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="C23" t="s">
         <v>37</v>
@@ -1304,12 +1467,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row ht="13" r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="C24" t="s">
         <v>38</v>
@@ -1329,32 +1492,32 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:L12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.08984375" style="6" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="12.08984375" style="8" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="24.08984375" style="9" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="18.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="6.6328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="9.81640625" style="6" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="15.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="7.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="6.6328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="6.90625" style="6" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="45.1796875" style="8" customWidth="1" collapsed="1"/>
-    <col min="13" max="16384" width="8.7265625" style="6" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="6" width="6.08984375" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="8" width="12.08984375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="9" width="24.08984375" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="6" width="7.81640625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="6" width="18.453125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="6" width="6.6328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="6" width="9.81640625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="6" width="15.54296875" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="6" width="6.6328125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="6" width="6.90625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="8" width="45.1796875" collapsed="true"/>
+    <col min="13" max="16384" style="6" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1392,12 +1555,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>139</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>41</v>
@@ -1415,12 +1578,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>42</v>
@@ -1438,12 +1601,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>43</v>
@@ -1461,12 +1624,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>44</v>
@@ -1484,12 +1647,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>45</v>
@@ -1507,12 +1670,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>46</v>
@@ -1530,12 +1693,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>47</v>
@@ -1553,12 +1716,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>48</v>
@@ -1579,12 +1742,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>49</v>
@@ -1605,12 +1768,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>50</v>
@@ -1631,12 +1794,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>149</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>51</v>
@@ -1658,7 +1821,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{9DAC9DAD-98AD-4914-90B7-E2BB443F241E}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{E70241B0-CD71-4DF8-B024-240F33CB00A7}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
+    <workbookView activeTab="2" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
   </bookViews>
   <sheets>
     <sheet name="BFLU" r:id="rId1" sheetId="1"/>
     <sheet name="BFLUError" r:id="rId2" sheetId="2"/>
+    <sheet name="BFLU_1Result" r:id="rId3" sheetId="3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="106">
   <si>
     <t>Result</t>
   </si>
@@ -227,268 +228,136 @@
     <t>aad123</t>
   </si>
   <si>
-    <t>Wed Mar 25 16:26:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:26:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:27:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:27:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:28:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:29:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:29:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:30:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:30:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:31:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:31:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:32:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:33:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:33:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:34:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:34:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:35:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:35:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:36:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:36:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:37:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:37:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:38:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:39:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:39:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:40:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:40:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:41:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:41:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:42:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:42:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:43:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:47:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 16:54:29 IST 2026</t>
+    <t>Thu Jun 18 02:37:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:38:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:39:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:40:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:41:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:42:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:43:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:44:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:45:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:46:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:47:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:48:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:49:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:49:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:50:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:51:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:52:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:53:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:54:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:55:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:56:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:56:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:57:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:58:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:59:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:59:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:00:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:01:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:01:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:02:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:03:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:04:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:04:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:05:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Payment app+ 1st + 2nd +3rd lookup</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:39:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Payment app+ Company Name</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:40:40 IST 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment app+ CAN </t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 20:17:36 IST 2026</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 12:50:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 12:53:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 12:56:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 12:59:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 13:02:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 13:05:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 13:08:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 13:11:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 13:14:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 13:17:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 13:21:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 13:25:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 13:30:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 13:33:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 13:37:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 13:40:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 13:44:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 13:47:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:03:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:04:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:05:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:06:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:06:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:07:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:08:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:08:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:09:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:10:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:10:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:11:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:12:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:12:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:13:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:14:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:14:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:15:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:15:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:16:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:17:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:17:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:18:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:18:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:19:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:20:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:21:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:21:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:22:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:22:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:23:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:23:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:24:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:24:59 IST 2026</t>
+    <t>Thu Jun 18 20:23:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 22:45:45 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -556,7 +425,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment wrapText="1"/>
@@ -582,6 +451,9 @@
     </xf>
     <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -972,7 +844,7 @@
         <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
@@ -992,7 +864,7 @@
         <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -1012,7 +884,7 @@
         <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -1032,7 +904,7 @@
         <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -1052,7 +924,7 @@
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
@@ -1072,7 +944,7 @@
         <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
@@ -1092,7 +964,7 @@
         <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
         <v>33</v>
@@ -1112,7 +984,7 @@
         <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
         <v>22</v>
@@ -1135,7 +1007,7 @@
         <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
@@ -1158,7 +1030,7 @@
         <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
@@ -1181,7 +1053,7 @@
         <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>25</v>
@@ -1207,7 +1079,7 @@
         <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>127</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
         <v>16</v>
@@ -1242,7 +1114,7 @@
         <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
@@ -1265,7 +1137,7 @@
         <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
         <v>26</v>
@@ -1288,7 +1160,7 @@
         <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>27</v>
@@ -1311,7 +1183,7 @@
         <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
         <v>29</v>
@@ -1334,7 +1206,7 @@
         <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
@@ -1357,7 +1229,7 @@
         <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -1380,7 +1252,7 @@
         <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
         <v>34</v>
@@ -1403,7 +1275,7 @@
         <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
         <v>35</v>
@@ -1426,7 +1298,7 @@
         <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
         <v>36</v>
@@ -1449,7 +1321,7 @@
         <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
         <v>37</v>
@@ -1472,7 +1344,7 @@
         <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
         <v>38</v>
@@ -1560,7 +1432,7 @@
         <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>41</v>
@@ -1583,7 +1455,7 @@
         <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>42</v>
@@ -1606,7 +1478,7 @@
         <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>87</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>43</v>
@@ -1629,7 +1501,7 @@
         <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>88</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>44</v>
@@ -1652,7 +1524,7 @@
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>89</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>45</v>
@@ -1675,7 +1547,7 @@
         <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>46</v>
@@ -1698,7 +1570,7 @@
         <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>47</v>
@@ -1721,7 +1593,7 @@
         <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>146</v>
+        <v>92</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>48</v>
@@ -1747,7 +1619,7 @@
         <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>147</v>
+        <v>93</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>49</v>
@@ -1773,7 +1645,7 @@
         <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>50</v>
@@ -1799,7 +1671,7 @@
         <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>51</v>
@@ -1824,4 +1696,115 @@
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CC679D0-D6B5-4D27-A6FC-900B976146EF}">
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="6" width="6.0" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="6" width="13.90625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="6" width="34.54296875" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="6" width="8.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="6" width="25.1796875" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="6" width="14.453125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="6" width="10.54296875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="6" width="21.453125" collapsed="true"/>
+    <col min="9" max="10" customWidth="true" style="6" width="14.90625" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="6" width="13.36328125" collapsed="true"/>
+    <col min="12" max="16384" style="6" width="8.7265625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="13" r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+    </row>
+    <row ht="13" r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="10"/>
+    </row>
+    <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="6">
+        <v>50020006</v>
+      </c>
+      <c r="K4" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="141">
   <si>
     <t>Result</t>
   </si>
@@ -358,6 +358,111 @@
   </si>
   <si>
     <t>Thu Jun 18 22:45:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 15:49:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 15:50:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 15:51:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 15:52:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 15:53:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 15:53:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 15:54:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 15:55:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 15:56:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 15:56:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 15:57:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 15:58:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 15:59:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 15:59:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:00:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:01:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:01:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:02:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:03:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:03:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:04:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:05:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:05:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:06:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:06:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:07:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:08:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:08:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:09:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:09:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:10:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:11:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:11:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:12:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:13:10 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -789,7 +894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="6.36328125" collapsed="true"/>
@@ -840,525 +945,525 @@
       </c>
     </row>
     <row ht="13" r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="0">
         <v>50020006</v>
       </c>
     </row>
     <row ht="13" r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="A4" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" t="s" s="0">
         <v>12</v>
       </c>
     </row>
     <row ht="13" r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="A5" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="C5" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" t="s" s="0">
         <v>13</v>
       </c>
     </row>
     <row ht="13" r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="A6" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="0">
         <v>282719</v>
       </c>
     </row>
     <row ht="13" r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="A7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="C7" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="0">
         <v>884777</v>
       </c>
     </row>
     <row ht="13" r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="A8" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="C8" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="0">
         <v>915029</v>
       </c>
     </row>
     <row ht="13" r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="A9" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="C9" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="0">
         <v>282719</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="0">
         <v>884777</v>
       </c>
     </row>
     <row ht="13" r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="A10" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="C10" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="0">
         <v>282719</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="0">
         <v>915029</v>
       </c>
     </row>
     <row ht="13" r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="A11" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="C11" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="0">
         <v>884777</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="0">
         <v>915029</v>
       </c>
     </row>
     <row ht="25.5" r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
+      <c r="A12" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>116</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="0">
         <v>282719</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="0">
         <v>884777</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="0">
         <v>915029</v>
       </c>
     </row>
     <row ht="13" r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="A13" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="C13" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="0">
         <v>50020006</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="0">
         <v>282719</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="0">
         <v>884777</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="0">
         <v>915029</v>
       </c>
     </row>
     <row ht="13" r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="A14" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="C14" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="0">
         <v>50020006</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row ht="13" r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="A15" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="C15" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" t="s" s="0">
         <v>13</v>
       </c>
     </row>
     <row ht="25.5" r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" t="s">
-        <v>76</v>
+      <c r="A16" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" t="s" s="0">
         <v>12</v>
       </c>
     </row>
     <row ht="13" r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="A17" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="C17" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="0">
         <v>282719</v>
       </c>
     </row>
     <row ht="13" r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="A18" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C18" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="0">
         <v>884777</v>
       </c>
     </row>
     <row ht="13" r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="A19" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="C19" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="0">
         <v>915029</v>
       </c>
     </row>
     <row ht="13" r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="A20" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="C20" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="0">
         <v>50020006</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="0">
         <v>282719</v>
       </c>
     </row>
     <row ht="13" r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="A21" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="C21" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="0">
         <v>50020006</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="0">
         <v>884777</v>
       </c>
     </row>
     <row ht="13" r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="A22" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="C22" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="0">
         <v>50020006</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="0">
         <v>915029</v>
       </c>
     </row>
     <row ht="13" r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="A23" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C23" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="0">
         <v>50020006</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" t="s" s="0">
         <v>12</v>
       </c>
     </row>
     <row ht="13" r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="A24" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="C24" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" t="s" s="0">
         <v>4</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="0">
         <v>50020006</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" t="s" s="0">
         <v>13</v>
       </c>
     </row>
@@ -1371,7 +1476,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="6" width="6.08984375" collapsed="true"/>
@@ -1428,11 +1533,11 @@
       </c>
     </row>
     <row ht="25" r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" t="s">
-        <v>85</v>
+      <c r="A2" t="s" s="6">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s" s="8">
+        <v>130</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>41</v>
@@ -1451,11 +1556,11 @@
       </c>
     </row>
     <row ht="25" r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" t="s">
-        <v>86</v>
+      <c r="A3" t="s" s="6">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s" s="8">
+        <v>131</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>42</v>
@@ -1474,11 +1579,11 @@
       </c>
     </row>
     <row ht="25" r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" t="s">
-        <v>87</v>
+      <c r="A4" t="s" s="6">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s" s="8">
+        <v>132</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>43</v>
@@ -1497,11 +1602,11 @@
       </c>
     </row>
     <row ht="25" r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" t="s">
-        <v>88</v>
+      <c r="A5" t="s" s="6">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s" s="8">
+        <v>133</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>44</v>
@@ -1520,11 +1625,11 @@
       </c>
     </row>
     <row ht="25" r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" t="s">
-        <v>89</v>
+      <c r="A6" t="s" s="6">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s" s="8">
+        <v>134</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>45</v>
@@ -1543,11 +1648,11 @@
       </c>
     </row>
     <row ht="25" r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" t="s">
-        <v>90</v>
+      <c r="A7" t="s" s="6">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s" s="8">
+        <v>135</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>46</v>
@@ -1566,11 +1671,11 @@
       </c>
     </row>
     <row ht="25" r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" t="s">
-        <v>91</v>
+      <c r="A8" t="s" s="6">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s" s="8">
+        <v>136</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>47</v>
@@ -1589,11 +1694,11 @@
       </c>
     </row>
     <row ht="37.5" r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" t="s">
-        <v>92</v>
+      <c r="A9" t="s" s="6">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s" s="8">
+        <v>137</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>48</v>
@@ -1615,11 +1720,11 @@
       </c>
     </row>
     <row ht="25" r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" t="s">
-        <v>93</v>
+      <c r="A10" t="s" s="6">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s" s="8">
+        <v>138</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>49</v>
@@ -1641,11 +1746,11 @@
       </c>
     </row>
     <row ht="37.5" r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" t="s">
-        <v>94</v>
+      <c r="A11" t="s" s="6">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s" s="8">
+        <v>139</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>50</v>
@@ -1667,11 +1772,11 @@
       </c>
     </row>
     <row ht="37.5" r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" t="s">
-        <v>95</v>
+      <c r="A12" t="s" s="6">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s" s="8">
+        <v>140</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>51</v>
@@ -1700,7 +1805,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CC679D0-D6B5-4D27-A6FC-900B976146EF}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="6" width="6.0" collapsed="true"/>
@@ -1752,10 +1857,10 @@
       </c>
     </row>
     <row ht="13" r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="6">
         <v>101</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="6">
         <v>102</v>
       </c>
       <c r="C2" s="9" t="s">
@@ -1784,11 +1889,11 @@
       <c r="K3" s="10"/>
     </row>
     <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" t="s">
-        <v>105</v>
+      <c r="A4" t="s" s="6">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s" s="6">
+        <v>129</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>100</v>

--- a/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="166">
   <si>
     <t>Result</t>
   </si>
@@ -463,6 +463,81 @@
   </si>
   <si>
     <t>Thu Jul 09 16:13:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 20:57:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 20:57:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:52:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:53:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:54:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:54:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:55:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:55:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:56:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:56:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:57:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:57:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:58:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:58:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:59:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:59:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 18 00:00:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 18 00:00:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 18 00:01:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 18 00:01:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 18 00:02:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 18 00:02:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 18 00:03:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 18 00:03:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 18 00:04:26 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -949,7 +1024,7 @@
         <v>52</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>17</v>
@@ -969,7 +1044,7 @@
         <v>52</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>18</v>
@@ -989,7 +1064,7 @@
         <v>52</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>19</v>
@@ -1009,7 +1084,7 @@
         <v>52</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>20</v>
@@ -1029,7 +1104,7 @@
         <v>52</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>21</v>
@@ -1049,7 +1124,7 @@
         <v>52</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="C7" t="s" s="0">
         <v>32</v>
@@ -1069,7 +1144,7 @@
         <v>52</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="C8" t="s" s="0">
         <v>33</v>
@@ -1089,7 +1164,7 @@
         <v>52</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="C9" t="s" s="0">
         <v>22</v>
@@ -1112,7 +1187,7 @@
         <v>52</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="C10" t="s" s="0">
         <v>23</v>
@@ -1135,7 +1210,7 @@
         <v>52</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>24</v>
@@ -1158,7 +1233,7 @@
         <v>52</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>25</v>
@@ -1184,7 +1259,7 @@
         <v>52</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="C13" t="s" s="0">
         <v>16</v>
@@ -1219,7 +1294,7 @@
         <v>52</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="C14" t="s" s="0">
         <v>28</v>
@@ -1242,7 +1317,7 @@
         <v>52</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="C15" t="s" s="0">
         <v>26</v>
@@ -1265,7 +1340,7 @@
         <v>52</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>27</v>
@@ -1288,7 +1363,7 @@
         <v>52</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="C17" t="s" s="0">
         <v>29</v>
@@ -1311,7 +1386,7 @@
         <v>52</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="C18" t="s" s="0">
         <v>30</v>
@@ -1334,7 +1409,7 @@
         <v>52</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="C19" t="s" s="0">
         <v>31</v>
@@ -1357,7 +1432,7 @@
         <v>52</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="C20" t="s" s="0">
         <v>34</v>
@@ -1380,7 +1455,7 @@
         <v>52</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="C21" t="s" s="0">
         <v>35</v>
@@ -1403,7 +1478,7 @@
         <v>52</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="C22" t="s" s="0">
         <v>36</v>
@@ -1426,7 +1501,7 @@
         <v>52</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="C23" t="s" s="0">
         <v>37</v>
@@ -1449,7 +1524,7 @@
         <v>52</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="C24" t="s" s="0">
         <v>38</v>
